--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_case_study_exports.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_case_study_exports.xlsx
@@ -811,17 +811,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -921,17 +921,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2241,17 +2241,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2571,17 +2571,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4221,17 +4221,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4771,17 +4771,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q38" t="n">
@@ -4881,17 +4881,17 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -5541,17 +5541,17 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -5651,17 +5651,17 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -5761,17 +5761,17 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -5871,17 +5871,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -5981,17 +5981,17 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -6201,17 +6201,17 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -6531,17 +6531,17 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -6971,17 +6971,17 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -7081,17 +7081,17 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -7191,17 +7191,17 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -7301,17 +7301,17 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q61" t="n">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -7521,17 +7521,17 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -7631,17 +7631,17 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -7741,17 +7741,17 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q65" t="n">
@@ -7851,17 +7851,17 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -7961,17 +7961,17 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -8181,17 +8181,17 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q69" t="n">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -8401,17 +8401,17 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -8621,17 +8621,17 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -8731,17 +8731,17 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q74" t="n">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -8951,17 +8951,17 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -9061,17 +9061,17 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -9171,17 +9171,17 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -9281,17 +9281,17 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -9391,17 +9391,17 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -9501,17 +9501,17 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -9611,17 +9611,17 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -9721,17 +9721,17 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -9831,17 +9831,17 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q84" t="n">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -10051,17 +10051,17 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q86" t="n">
@@ -10161,17 +10161,17 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q87" t="n">
@@ -10271,17 +10271,17 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q88" t="n">
@@ -10381,17 +10381,17 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q89" t="n">
@@ -10491,17 +10491,17 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q90" t="n">
@@ -10601,17 +10601,17 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -10711,17 +10711,17 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q92" t="n">
@@ -10821,17 +10821,17 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -10931,17 +10931,17 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -11041,17 +11041,17 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -11151,17 +11151,17 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -11261,17 +11261,17 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -11371,17 +11371,17 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -11481,17 +11481,17 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q99" t="n">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -11701,17 +11701,17 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -11811,17 +11811,17 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -11921,17 +11921,17 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q103" t="n">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -12141,17 +12141,17 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -12361,17 +12361,17 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -12471,17 +12471,17 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -12581,17 +12581,17 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -12691,17 +12691,17 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -12801,17 +12801,17 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -12911,17 +12911,17 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q112" t="n">
@@ -13021,17 +13021,17 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -13131,17 +13131,17 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -13241,17 +13241,17 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q115" t="n">
@@ -13351,17 +13351,17 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -13461,17 +13461,17 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q117" t="n">
@@ -13571,17 +13571,17 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -13681,17 +13681,17 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q119" t="n">
@@ -13791,17 +13791,17 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q120" t="n">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q121" t="n">
@@ -14011,17 +14011,17 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q122" t="n">
@@ -14121,17 +14121,17 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q123" t="n">
@@ -14231,17 +14231,17 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q124" t="n">
@@ -14341,17 +14341,17 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q125" t="n">
@@ -14451,17 +14451,17 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q126" t="n">
@@ -14561,17 +14561,17 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q127" t="n">
@@ -14671,17 +14671,17 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q128" t="n">
@@ -14781,17 +14781,17 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q129" t="n">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q130" t="n">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q131" t="n">
@@ -15111,17 +15111,17 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q132" t="n">
@@ -15221,17 +15221,17 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q133" t="n">
@@ -15331,17 +15331,17 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q134" t="n">
@@ -15441,17 +15441,17 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q135" t="n">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q136" t="n">
@@ -15661,17 +15661,17 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q137" t="n">
@@ -15771,17 +15771,17 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q138" t="n">
@@ -15881,17 +15881,17 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -15991,17 +15991,17 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q140" t="n">
@@ -16101,17 +16101,17 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q141" t="n">
@@ -16211,17 +16211,17 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q142" t="n">
@@ -16321,17 +16321,17 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q143" t="n">
@@ -16431,17 +16431,17 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q144" t="n">
@@ -16541,17 +16541,17 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q145" t="n">
@@ -16651,17 +16651,17 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q146" t="n">
@@ -16761,17 +16761,17 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q147" t="n">
@@ -16871,17 +16871,17 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q148" t="n">
@@ -16981,17 +16981,17 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q149" t="n">
@@ -17091,17 +17091,17 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q150" t="n">
@@ -17201,17 +17201,17 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q151" t="n">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q152" t="n">
@@ -17421,17 +17421,17 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q153" t="n">
@@ -17531,17 +17531,17 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q154" t="n">
@@ -17641,17 +17641,17 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q155" t="n">
@@ -17751,17 +17751,17 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q156" t="n">
@@ -17861,17 +17861,17 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q157" t="n">
@@ -17971,17 +17971,17 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q158" t="n">
@@ -18081,17 +18081,17 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q159" t="n">
@@ -18191,17 +18191,17 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q160" t="n">
@@ -18301,17 +18301,17 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q161" t="n">
@@ -18411,17 +18411,17 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q162" t="n">
@@ -18521,17 +18521,17 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q163" t="n">
@@ -18631,17 +18631,17 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q164" t="n">
@@ -18741,17 +18741,17 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q165" t="n">
@@ -18851,17 +18851,17 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q166" t="n">
@@ -18961,17 +18961,17 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q167" t="n">
@@ -19071,17 +19071,17 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q168" t="n">
@@ -19181,17 +19181,17 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q169" t="n">
@@ -19291,17 +19291,17 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q170" t="n">
@@ -19401,17 +19401,17 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q171" t="n">
@@ -19511,17 +19511,17 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q172" t="n">
@@ -19621,17 +19621,17 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q173" t="n">
@@ -19731,17 +19731,17 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q174" t="n">
@@ -19841,17 +19841,17 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q175" t="n">
@@ -19951,17 +19951,17 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q176" t="n">
@@ -20061,17 +20061,17 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q177" t="n">
@@ -20171,17 +20171,17 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q178" t="n">
@@ -20281,17 +20281,17 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q179" t="n">
@@ -20391,17 +20391,17 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q180" t="n">
@@ -20501,17 +20501,17 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q181" t="n">
@@ -20611,17 +20611,17 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q182" t="n">
@@ -20721,17 +20721,17 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q183" t="n">
@@ -20831,17 +20831,17 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q184" t="n">
@@ -20941,17 +20941,17 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q185" t="n">
@@ -21051,17 +21051,17 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q186" t="n">
@@ -21161,17 +21161,17 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q187" t="n">
@@ -21271,17 +21271,17 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q188" t="n">
@@ -21381,17 +21381,17 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q189" t="n">
@@ -21491,17 +21491,17 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q190" t="n">
@@ -21601,17 +21601,17 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q191" t="n">
@@ -21711,17 +21711,17 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q192" t="n">
@@ -21821,17 +21821,17 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q193" t="n">
@@ -21931,17 +21931,17 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q194" t="n">
@@ -22041,17 +22041,17 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q195" t="n">
@@ -22151,17 +22151,17 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q196" t="n">
@@ -22261,17 +22261,17 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T020233Z</t>
+          <t>D7-LOCAL-20260726T032027Z</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="Q197" t="n">

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_case_study_exports.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_case_study_exports.xlsx
@@ -599,7 +599,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
     <col width="45" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -781,7 +781,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9831,12 +9831,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10381,12 +10381,12 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10491,12 +10491,12 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -11701,12 +11701,12 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -12581,12 +12581,12 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -12691,12 +12691,12 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -12801,12 +12801,12 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -13571,12 +13571,12 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -14121,12 +14121,12 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -14231,12 +14231,12 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14561,12 +14561,12 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -15111,12 +15111,12 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15221,12 +15221,12 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -15441,12 +15441,12 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15551,12 +15551,12 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -15661,12 +15661,12 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -15771,12 +15771,12 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -15881,12 +15881,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -15991,12 +15991,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -16211,12 +16211,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -16321,12 +16321,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -16431,12 +16431,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -16651,12 +16651,12 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -16761,12 +16761,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -16871,12 +16871,12 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -17091,12 +17091,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17281,7 +17281,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17391,7 +17391,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -17421,12 +17421,12 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17641,12 +17641,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17751,12 +17751,12 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17861,12 +17861,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -17971,12 +17971,12 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18191,12 +18191,12 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18411,12 +18411,12 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18521,12 +18521,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18631,12 +18631,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19071,12 +19071,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19181,12 +19181,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -19291,12 +19291,12 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19401,12 +19401,12 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19621,12 +19621,12 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -19731,12 +19731,12 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -19841,12 +19841,12 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -19951,12 +19951,12 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -20061,12 +20061,12 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -20171,12 +20171,12 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -20281,12 +20281,12 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -20361,7 +20361,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -20391,12 +20391,12 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -20501,12 +20501,12 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20581,7 +20581,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -20611,12 +20611,12 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -20721,12 +20721,12 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -20831,12 +20831,12 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20911,7 +20911,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -20941,12 +20941,12 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -21021,7 +21021,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -21051,12 +21051,12 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -21161,12 +21161,12 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -21271,12 +21271,12 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -21351,7 +21351,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -21381,12 +21381,12 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -21491,12 +21491,12 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -21601,12 +21601,12 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -21711,12 +21711,12 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -21821,12 +21821,12 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -21931,12 +21931,12 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -22041,12 +22041,12 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -22151,12 +22151,12 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -22261,12 +22261,12 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T032027Z</t>
+          <t>D7-LOCAL-20260726T051805Z</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_case_study_exports.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_case_study_exports.xlsx
@@ -599,7 +599,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
     <col width="45" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -811,12 +811,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9831,12 +9831,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9941,12 +9941,12 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10381,12 +10381,12 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10491,12 +10491,12 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -11701,12 +11701,12 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -12581,12 +12581,12 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -12691,12 +12691,12 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -12801,12 +12801,12 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -13571,12 +13571,12 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -13681,12 +13681,12 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -14121,12 +14121,12 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -14231,12 +14231,12 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -14561,12 +14561,12 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -14891,12 +14891,12 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -15001,12 +15001,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -15111,12 +15111,12 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -15221,12 +15221,12 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -15441,12 +15441,12 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -15551,12 +15551,12 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -15661,12 +15661,12 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -15771,12 +15771,12 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -15881,12 +15881,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -15991,12 +15991,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -16211,12 +16211,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -16321,12 +16321,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -16431,12 +16431,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -16651,12 +16651,12 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -16761,12 +16761,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -16871,12 +16871,12 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -17091,12 +17091,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -17421,12 +17421,12 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -17641,12 +17641,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -17751,12 +17751,12 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -17861,12 +17861,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -17971,12 +17971,12 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -18081,12 +18081,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -18191,12 +18191,12 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18301,12 +18301,12 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -18411,12 +18411,12 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -18521,12 +18521,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -18631,12 +18631,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19071,12 +19071,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19181,12 +19181,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -19291,12 +19291,12 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -19401,12 +19401,12 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -19621,12 +19621,12 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19731,12 +19731,12 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -19841,12 +19841,12 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -19951,12 +19951,12 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -20061,12 +20061,12 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -20171,12 +20171,12 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -20281,12 +20281,12 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -20391,12 +20391,12 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -20501,12 +20501,12 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20611,12 +20611,12 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -20721,12 +20721,12 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -20831,12 +20831,12 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -20941,12 +20941,12 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -21051,12 +21051,12 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -21161,12 +21161,12 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -21271,12 +21271,12 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -21381,12 +21381,12 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -21491,12 +21491,12 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -21601,12 +21601,12 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -21711,12 +21711,12 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21821,12 +21821,12 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21931,12 +21931,12 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -22041,12 +22041,12 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -22151,12 +22151,12 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -22261,12 +22261,12 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>D7-LOCAL-20260726T051805Z</t>
+          <t>D7-LOCAL-20260726T074210Z</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
